--- a/Companion-Workbooks/Risk_Register_Workbook.xlsx
+++ b/Companion-Workbooks/Risk_Register_Workbook.xlsx
@@ -2971,7 +2971,7 @@
       </c>
       <c r="H3" s="57" t="inlineStr">
         <is>
-          <t>NF-CW1  ·  v1.0</t>
+          <t>NF-CW1  ·  v2.0</t>
         </is>
       </c>
     </row>
@@ -2998,14 +2998,14 @@
     <row r="11" ht="46" customHeight="1" s="55">
       <c r="B11" s="60" t="inlineStr">
         <is>
-          <t>The Row That Wasn’t There</t>
+          <t>The Norwood Files</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="55">
       <c r="B12" s="61" t="inlineStr">
         <is>
-          <t>A Novel About Process Risk, Corrective Action and the Register That Missed the Factory</t>
+          <t>A Novel About Risk, Audit and Root Cause in a Factory That Stopped Pretending</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
     <row r="15" ht="26" customHeight="1" s="55">
       <c r="B15" s="62" t="inlineStr">
         <is>
-          <t>Companion to Book One</t>
+          <t>Companion to Part One — The Register</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C21" s="66" t="inlineStr">
         <is>
-          <t>v1.0  ·  NF-CW1</t>
+          <t>v2.0  ·  NF-CW1</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="C23" s="66" t="inlineStr">
         <is>
-          <t>Matches the first edition of the book (Editorial Baseline EBL-3.1)</t>
+          <t>Matches the omnibus first edition of The Norwood Files (build RC-Rev9)</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="C24" s="66" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>29 August 2026</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW1 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3682,7 +3682,7 @@
         <v/>
       </c>
       <c r="I5" s="124">
-        <f>IFERROR(1-SUM('Form 2 Risk Register'!R5:R204)/SUM('Form 2 Risk Register'!K5:K204),"")</f>
+        <f>IFERROR(1-SUM('Form 2 Risk Register'!R5:R204)/SUMIF('Form 2 Risk Register'!R5:R204,"&gt;0",'Form 2 Risk Register'!K5:K204),"")</f>
         <v/>
       </c>
     </row>
@@ -4125,7 +4125,7 @@
     <row r="79" ht="15" customHeight="1" s="55">
       <c r="A79" s="129" t="inlineStr">
         <is>
-          <t>3 Automated control</t>
+          <t>3 Automate control</t>
         </is>
       </c>
       <c r="B79" s="129">
@@ -4182,7 +4182,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW1 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4475,7 +4475,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW1 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4524,7 +4524,7 @@
     <row r="2" ht="15.75" customHeight="1" s="55">
       <c r="A2" s="87" t="inlineStr">
         <is>
-          <t>CNC machining of a cast-iron housing—complete worked register from Part 2. Read, do not edit.</t>
+          <t>CNC machining of a cast-iron housing—complete worked register from Part One. Read, do not edit.</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW1 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6535,7 +6535,7 @@
     <row r="2" ht="15.75" customHeight="1" s="55">
       <c r="A2" s="87" t="inlineStr">
         <is>
-          <t>Fusion-bonded epoxy pipe coating line—complete worked register from Part 2. Read, do not edit.</t>
+          <t>Fusion-bonded epoxy pipe coating line—complete worked register from Part One. Read, do not edit.</t>
         </is>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW1 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8397,7 +8397,7 @@
     <row r="2" ht="15.75" customHeight="1" s="55">
       <c r="A2" s="87" t="inlineStr">
         <is>
-          <t>Hydraulic cylinder assembly and pressure test—complete worked register from Part 2. Read, do not edit.</t>
+          <t>Hydraulic cylinder assembly and pressure test—complete worked register from Part One. Read, do not edit.</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW1 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -10171,7 +10171,7 @@
     <row r="7" ht="15" customHeight="1" s="55">
       <c r="B7" s="139" t="inlineStr">
         <is>
-          <t>Companion to Book One</t>
+          <t>Companion to Part One</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
     <row r="9" ht="15" customHeight="1" s="55">
       <c r="B9" s="140" t="inlineStr">
         <is>
-          <t>Document code: NF-CW1 · Identity: NBSM v1.0 · Baseline: EBL-3.1 · Issued 22 August 2026</t>
+          <t>Document code: NF-CW1 · Identity: NBSM v1.0 · Baseline: RC-Rev9 · Issued 29 August 2026</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="H2" s="57" t="inlineStr">
         <is>
-          <t>NF-CW1  ·  v1.0</t>
+          <t>NF-CW1  ·  v2.0</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
     <row r="8" ht="14" customHeight="1" s="55">
       <c r="B8" s="70" t="inlineStr">
         <is>
-          <t>This workbook is the working half of Book One of The Norwood Files. It carries the forms from the book with the rules already written into the formulas, so that the method can be run on a real process instead of read about. Its subject is building and operating a process risk register: process flow, calibrated scales, the trigger rule, the action hierarchy, effectiveness verification and supplier risk.</t>
+          <t>This workbook is the working half of Part One of The Norwood Files. It carries the forms from the book with the rules already written into the formulas, so that the method can be run on a real process instead of read about. Its subject is building and operating a process risk register: process flow, calibrated scales, the trigger rule, the action hierarchy, effectiveness verification and supplier risk.</t>
         </is>
       </c>
     </row>
@@ -10785,7 +10785,7 @@
       </c>
       <c r="H2" s="57" t="inlineStr">
         <is>
-          <t>NF-CW1  ·  v1.0</t>
+          <t>NF-CW1  ·  v2.0</t>
         </is>
       </c>
     </row>
@@ -10838,7 +10838,7 @@
       <c r="C9" s="64" t="n"/>
       <c r="D9" s="82" t="inlineStr">
         <is>
-          <t>The Norwood Files — Companion to Book One</t>
+          <t>The Norwood Files — Companion to Part One</t>
         </is>
       </c>
       <c r="E9" s="64" t="n"/>
@@ -10855,7 +10855,7 @@
       <c r="C10" s="64" t="n"/>
       <c r="D10" s="82" t="inlineStr">
         <is>
-          <t>The Row That Wasn’t There</t>
+          <t>The Norwood Files</t>
         </is>
       </c>
       <c r="E10" s="64" t="n"/>
@@ -10889,7 +10889,7 @@
       <c r="C12" s="64" t="n"/>
       <c r="D12" s="82" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v2.0</t>
         </is>
       </c>
       <c r="E12" s="64" t="n"/>
@@ -10906,7 +10906,7 @@
       <c r="C13" s="64" t="n"/>
       <c r="D13" s="82" t="inlineStr">
         <is>
-          <t>v1.0  ·  issued 22 August 2026</t>
+          <t>v2.0  ·  issued 29 August 2026</t>
         </is>
       </c>
       <c r="E13" s="64" t="n"/>
@@ -10940,7 +10940,7 @@
       <c r="C15" s="64" t="n"/>
       <c r="D15" s="82" t="inlineStr">
         <is>
-          <t>EBL-3.1</t>
+          <t>RC-Rev9</t>
         </is>
       </c>
       <c r="E15" s="64" t="n"/>
@@ -11014,7 +11014,7 @@
     <row r="27" ht="13" customHeight="1" s="55">
       <c r="B27" s="83" t="inlineStr">
         <is>
-          <t>This workbook accompanies The Row That Wasn’t There and is supplied free of charge with the book. You may use it, adapt it and reproduce it inside your own organization for your own quality management system.</t>
+          <t>This workbook accompanies The Norwood Files and is supplied free of charge with the book. You may use it, adapt it and reproduce it inside your own organization for your own quality management system.</t>
         </is>
       </c>
     </row>
@@ -11115,7 +11115,7 @@
     <row r="1" ht="25.5" customHeight="1" s="55">
       <c r="A1" s="86" t="inlineStr">
         <is>
-          <t>PROCESS RISK ANALYSIS AND CORRECTIVE ACTION</t>
+          <t>THE NORWOOD FILES — PART ONE COMPANION</t>
         </is>
       </c>
     </row>
@@ -11137,7 +11137,7 @@
     <row r="5" ht="25.5" customHeight="1" s="55">
       <c r="B5" s="89" t="inlineStr">
         <is>
-          <t>The forms from Part 3 of the book, with the trigger rule already written into the formulas, plus the three worked registers from Part 2 as completed examples.</t>
+          <t>The forms from Part Five of the book, with the trigger rule already written into the formulas, plus the three worked registers from Part One as completed examples.</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
     <row r="20" ht="39" customHeight="1" s="55">
       <c r="B20" s="89" t="inlineStr">
         <is>
-          <t>The numbered sheets carry the same Form numbers as Part 3 of the book. Form 3 in the book is Form 3 in this file. The Rating Scales sheet is section 3.2 of the book and is deliberately unnumbered.</t>
+          <t>The numbered sheets carry the same Form numbers as Part Five of the book. Form 3 in the book is Form 3 in this file. The Rating Scales sheet is section 5.2 of the book and is deliberately unnumbered.</t>
         </is>
       </c>
     </row>
@@ -11263,7 +11263,7 @@
     <row r="23" ht="15" customHeight="1" s="55">
       <c r="A23" s="88" t="inlineStr">
         <is>
-          <t>CELL COLOURS</t>
+          <t>CELL COLORS</t>
         </is>
       </c>
     </row>
@@ -11278,7 +11278,7 @@
     <row r="26" ht="15" customHeight="1" s="55">
       <c r="A26" s="90" t="inlineStr">
         <is>
-          <t>The Norwood Files · Companion to Book One · v1.0 · issued 22 August 2026 · matches the first edition (Editorial Baseline EBL-3.1)</t>
+          <t>The Norwood Files · Companion to Part One · v2.0 · issued 29 August 2026 · matches the omnibus first edition (build RC-Rev9)</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11293,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW1 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -11650,7 +11650,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW1 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -11759,6 +11759,16 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" s="55">
+      <c r="G6" s="98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H6" s="99" t="inlineStr">
+        <is>
+          <t>No control. Found by the customer, or not at all.</t>
+        </is>
+      </c>
       <c r="A6" s="98" t="inlineStr">
         <is>
           <t>10</t>
@@ -11773,19 +11783,19 @@
       </c>
       <c r="E6" s="93" t="n"/>
       <c r="F6" s="93" t="n"/>
-      <c r="G6" s="98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H6" s="99" t="inlineStr">
-        <is>
-          <t>No control. Found by the customer, or not at all.</t>
-        </is>
-      </c>
       <c r="I6" s="93" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1" s="55">
+      <c r="G7" s="98" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="99" t="inlineStr">
+        <is>
+          <t>No control at this step. Anything that finds it does so downstream, by chance.</t>
+        </is>
+      </c>
       <c r="A7" s="98" t="inlineStr">
         <is>
           <t>9</t>
@@ -11800,19 +11810,19 @@
       </c>
       <c r="E7" s="93" t="n"/>
       <c r="F7" s="93" t="n"/>
-      <c r="G7" s="98" t="inlineStr">
+      <c r="I7" s="93" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" s="55">
+      <c r="G8" s="98" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H7" s="99" t="inlineStr">
+      <c r="H8" s="99" t="inlineStr">
         <is>
           <t>Found downstream, or by the next process owner.</t>
         </is>
       </c>
-      <c r="I7" s="93" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1" s="55">
       <c r="A8" s="98" t="inlineStr">
         <is>
           <t>7–8</t>
@@ -11827,19 +11837,19 @@
       </c>
       <c r="E8" s="93" t="n"/>
       <c r="F8" s="93" t="n"/>
-      <c r="G8" s="98" t="inlineStr">
+      <c r="I8" s="93" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1" s="55">
+      <c r="G9" s="98" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H8" s="99" t="inlineStr">
+      <c r="H9" s="99" t="inlineStr">
         <is>
           <t>Operator visual or judgment. No record.</t>
         </is>
       </c>
-      <c r="I8" s="93" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="55">
       <c r="A9" s="98" t="inlineStr">
         <is>
           <t>5–6</t>
@@ -11854,19 +11864,19 @@
       </c>
       <c r="E9" s="93" t="n"/>
       <c r="F9" s="93" t="n"/>
-      <c r="G9" s="98" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H9" s="99" t="inlineStr">
-        <is>
-          <t>100% final inspection, manual, recorded.</t>
-        </is>
-      </c>
       <c r="I9" s="93" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1" s="55">
+      <c r="G10" s="98" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="99" t="inlineStr">
+        <is>
+          <t>Manual check on a sample or at a handover, with a record or a signature.</t>
+        </is>
+      </c>
       <c r="A10" s="98" t="inlineStr">
         <is>
           <t>3–4</t>
@@ -11881,19 +11891,19 @@
       </c>
       <c r="E10" s="93" t="n"/>
       <c r="F10" s="93" t="n"/>
-      <c r="G10" s="98" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="99" t="inlineStr">
-        <is>
-          <t>Sample-based automated test.</t>
-        </is>
-      </c>
       <c r="I10" s="93" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1" s="55">
+      <c r="G11" s="98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H11" s="99" t="inlineStr">
+        <is>
+          <t>100% final inspection, manual, recorded.</t>
+        </is>
+      </c>
       <c r="A11" s="98" t="inlineStr">
         <is>
           <t>1–2</t>
@@ -11901,64 +11911,82 @@
       </c>
       <c r="B11" s="93" t="n"/>
       <c r="C11" s="93" t="n"/>
-      <c r="G11" s="98" t="inlineStr">
+      <c r="I11" s="93" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="55">
+      <c r="G12" s="98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H12" s="99" t="inlineStr">
+        <is>
+          <t>Sample-based automated test.</t>
+        </is>
+      </c>
+      <c r="D12" s="100" t="inlineStr">
+        <is>
+          <t>Anchor on your own data. Scrap taken at the machine is usually not in the NCR log—tally it for four weeks first.</t>
+        </is>
+      </c>
+      <c r="I12" s="93" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="55">
+      <c r="G13" s="98" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H11" s="99" t="inlineStr">
+      <c r="H13" s="99" t="inlineStr">
         <is>
           <t>100% automated in process, recorded per part.</t>
         </is>
       </c>
-      <c r="I11" s="93" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="55">
-      <c r="D12" s="100" t="inlineStr">
-        <is>
-          <t>Anchor on your own data. Scrap taken at the machine is usually not in the NCR log—tally it for four weeks first.</t>
-        </is>
-      </c>
-      <c r="G12" s="98" t="inlineStr">
+      <c r="A13" s="100" t="inlineStr">
+        <is>
+          <t>The most useful question is rarely 'how bad is the damage' but 'who finds it, and when'.</t>
+        </is>
+      </c>
+      <c r="I13" s="93" t="n"/>
+    </row>
+    <row r="14">
+      <c r="G14" s="98" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H12" s="99" t="inlineStr">
+      <c r="H14" s="99" t="inlineStr">
         <is>
           <t>Automated with alarm or automatic hold.</t>
         </is>
       </c>
-      <c r="I12" s="93" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1" s="55">
-      <c r="A13" s="100" t="inlineStr">
-        <is>
-          <t>The most useful question is rarely 'how bad is the damage' but 'who finds it, and when'.</t>
-        </is>
-      </c>
-      <c r="G13" s="98" t="inlineStr">
+    </row>
+    <row r="15" ht="30" customHeight="1" s="55">
+      <c r="G15" s="98" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H13" s="99" t="inlineStr">
+      <c r="H15" s="99" t="inlineStr">
         <is>
           <t>Error-proofed. Cannot occur, or cannot pass.</t>
         </is>
       </c>
-      <c r="I13" s="93" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15" ht="30" customHeight="1" s="55">
-      <c r="G15" s="100" t="inlineStr">
+    </row>
+    <row r="16" ht="30" customHeight="1" s="55">
+      <c r="G16" s="100" t="inlineStr">
         <is>
           <t>Rate the control running today, on the cell where the part actually runs. Find the record before you write the number.</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
+    <row r="17" ht="30" customHeight="1" s="55">
+      <c r="G17" s="100" t="inlineStr">
+        <is>
+          <t>Rate against this failure mode, not the control in general. The same visual check earns a 6 against a seal fitted the wrong way round and an 8 against particulate inside a bore. One label carrying the same number everywhere means you rated the control and not the failure.</t>
+        </is>
+      </c>
+    </row>
     <row r="18" ht="15" customHeight="1" s="55">
       <c r="A18" s="101" t="inlineStr">
         <is>
@@ -12044,7 +12072,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="A13:C13"/>
@@ -12057,14 +12085,15 @@
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G17:I17"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW1 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -18865,7 +18894,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW1 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -20674,7 +20703,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="D5:D124" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"1 Eliminate cause,2 Error-proof,3 Automated control,4 Detection,5 Procedure"</formula1>
+      <formula1>"1 Eliminate cause,2 Error-proof,3 Automate control,4 Detection,5 Procedure"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -20683,7 +20712,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW1 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -21093,7 +21122,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW1 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part One&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
